--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126441182</v>
+        <v>120116922</v>
       </c>
       <c r="B2" t="n">
-        <v>107441</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220107</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760021</v>
+        <v>760031</v>
       </c>
       <c r="R2" t="n">
-        <v>7093671</v>
+        <v>7093709</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,15 +764,112 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120116922</v>
+        <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760031</v>
+        <v>760091</v>
       </c>
       <c r="R2" t="n">
-        <v>7093709</v>
+        <v>7093644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,60 +778,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126441182</v>
+        <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>108201</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220107</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760021</v>
+        <v>760131</v>
       </c>
       <c r="R3" t="n">
-        <v>7093671</v>
+        <v>7093695</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +863,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla hack vid dike/bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,15 +898,1081 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135477692</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>760037</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7093670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120116922</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>760031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135477707</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760033</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135477742</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093703</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135477699</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135477700</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760117</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135477743</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760163</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,55 +672,64 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120116922</v>
+        <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760031</v>
+        <v>760091</v>
       </c>
       <c r="R2" t="n">
-        <v>7093709</v>
+        <v>7093644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,22 +783,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135542830</v>
+        <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,37 +811,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760062</v>
+        <v>760131</v>
       </c>
       <c r="R3" t="n">
-        <v>7093642</v>
+        <v>7093695</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,14 +888,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla hack vid dike/bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -880,13 +917,18 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126441182</v>
+        <v>135477692</v>
       </c>
       <c r="B4" t="n">
-        <v>108201</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +936,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220107</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760021</v>
+        <v>760037</v>
       </c>
       <c r="R4" t="n">
-        <v>7093671</v>
+        <v>7093670</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -948,12 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,17 +1028,1145 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477692</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120116922</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>760031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135542830</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brännvinsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760062</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135542830</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Andreas Schneider</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441182</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135477707</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760033</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477707</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135477742</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760136</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093703</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477742</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135477699</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760132</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477699</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135477700</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760117</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477700</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135477743</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760163</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135477692</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135542830</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>103764</v>
+        <v>103815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99504</v>
+        <v>99551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>103907</v>
+        <v>103958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>103815</v>
+        <v>103842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99551</v>
+        <v>99578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>103958</v>
+        <v>103985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120116922</v>
+        <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760031</v>
+        <v>760091</v>
       </c>
       <c r="R2" t="n">
-        <v>7093709</v>
+        <v>7093644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,65 +783,73 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135477693</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126441182</v>
+        <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>108201</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220107</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760021</v>
+        <v>760131</v>
       </c>
       <c r="R3" t="n">
-        <v>7093671</v>
+        <v>7093695</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +873,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla hack vid dike/bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,18 +908,1383 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135477698</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135477692</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>760037</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7093670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477692</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135456545</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58415</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännvinsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>760050</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7093705</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135456545</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120116922</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760031</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135542830</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännvinsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760062</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093642</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135542830</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126441182</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135477707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103847</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477707</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100886</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135477742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760136</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093703</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477742</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135477699</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99583</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760132</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477699</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135477700</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760117</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477700</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135477743</v>
+      </c>
+      <c r="B14" t="n">
+        <v>103990</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>760163</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477703</t>
         </is>
       </c>
     </row>
@@ -890,6 +2292,18 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -1505,7 +1505,7 @@
         <v>135477707</v>
       </c>
       <c r="B9" t="n">
-        <v>103847</v>
+        <v>103849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>135477706</v>
       </c>
       <c r="B10" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135477742</v>
       </c>
       <c r="B11" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>135477699</v>
       </c>
       <c r="B12" t="n">
-        <v>99583</v>
+        <v>99585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>135477700</v>
       </c>
       <c r="B13" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135477743</v>
       </c>
       <c r="B14" t="n">
-        <v>103990</v>
+        <v>103992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135477703</v>
       </c>
       <c r="B15" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135456545</v>
+        <v>120116922</v>
       </c>
       <c r="B5" t="n">
-        <v>58415</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,54 +1056,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760050</v>
+        <v>760031</v>
       </c>
       <c r="R5" t="n">
-        <v>7093705</v>
+        <v>7093709</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,27 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,69 +1134,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120116922</v>
+        <v>135542830</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760031</v>
+        <v>760062</v>
       </c>
       <c r="R6" t="n">
-        <v>7093709</v>
+        <v>7093642</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,19 +1216,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1271,65 +1246,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135542830</v>
+        <v>126441182</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>108201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220107</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760062</v>
+        <v>760021</v>
       </c>
       <c r="R7" t="n">
-        <v>7093642</v>
+        <v>7093671</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,29 +1328,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1383,44 +1348,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126441182</v>
+        <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>108201</v>
+        <v>103849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220107</v>
+        <v>222004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760021</v>
+        <v>760033</v>
       </c>
       <c r="R8" t="n">
-        <v>7093671</v>
+        <v>7093698</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,12 +1430,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1460,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477707</v>
+        <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>103849</v>
+        <v>100888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,16 +1488,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222004</v>
+        <v>222584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1537,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760033</v>
+        <v>760044</v>
       </c>
       <c r="R9" t="n">
-        <v>7093698</v>
+        <v>7093709</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,16 +1583,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477706</v>
+        <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>100888</v>
+        <v>99553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222584</v>
+        <v>222812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1649,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760044</v>
+        <v>760136</v>
       </c>
       <c r="R10" t="n">
-        <v>7093709</v>
+        <v>7093703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,22 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,16 +1695,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477742</v>
+        <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99553</v>
+        <v>99585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,34 +1712,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>222857</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760136</v>
+        <v>760132</v>
       </c>
       <c r="R11" t="n">
-        <v>7093703</v>
+        <v>7093698</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,22 +1770,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,16 +1811,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477699</v>
+        <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99585</v>
+        <v>99082</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,41 +1828,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760132</v>
+        <v>760117</v>
       </c>
       <c r="R12" t="n">
-        <v>7093698</v>
+        <v>7093700</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,16 +1923,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477700</v>
+        <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>99082</v>
+        <v>103992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,16 +1940,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223049</v>
+        <v>223284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760117</v>
+        <v>760163</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1994,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,16 +2035,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477743</v>
+        <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>103992</v>
+        <v>98327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223284</v>
+        <v>223358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760163</v>
+        <v>760075</v>
       </c>
       <c r="R14" t="n">
-        <v>7093700</v>
+        <v>7093751</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,22 +2106,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,118 +2146,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135477703</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>760075</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7093751</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2303,7 +2166,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,68 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135456545</v>
+        <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>58415</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760050</v>
+        <v>760091</v>
       </c>
       <c r="R2" t="n">
-        <v>7093705</v>
+        <v>7093644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,58 +794,62 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/135477693</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120116922</v>
+        <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760031</v>
+        <v>760131</v>
       </c>
       <c r="R3" t="n">
-        <v>7093709</v>
+        <v>7093695</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,12 +873,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla hack vid dike/bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,65 +908,73 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135477698</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135542830</v>
+        <v>135477692</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760062</v>
+        <v>760037</v>
       </c>
       <c r="R4" t="n">
-        <v>7093642</v>
+        <v>7093670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,14 +1013,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1029,16 +1039,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/135477692</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126441182</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>108201</v>
+        <v>58415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,37 +1056,57 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220107</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760021</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093671</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,18 +1165,1126 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135456545</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120116922</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760031</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135542830</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännvinsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760062</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093642</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135542830</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126441182</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135477707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103849</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477707</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100888</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135477742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99553</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760136</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093703</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477742</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135477699</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99585</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760132</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477699</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135477700</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760117</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477700</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135477743</v>
+      </c>
+      <c r="B14" t="n">
+        <v>103992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>760163</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477703</t>
         </is>
       </c>
     </row>
@@ -1141,6 +2294,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120116922</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,38 +1056,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760031</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093709</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,65 +1165,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135456545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135542830</v>
+        <v>120116922</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760062</v>
+        <v>760031</v>
       </c>
       <c r="R6" t="n">
-        <v>7093642</v>
+        <v>7093709</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,29 +1251,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1246,65 +1271,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126441182</v>
+        <v>135542830</v>
       </c>
       <c r="B7" t="n">
-        <v>108201</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220107</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760021</v>
+        <v>760062</v>
       </c>
       <c r="R7" t="n">
-        <v>7093671</v>
+        <v>7093642</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1353,29 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1348,44 +1383,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135477707</v>
+        <v>126441182</v>
       </c>
       <c r="B8" t="n">
-        <v>103849</v>
+        <v>108201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222004</v>
+        <v>220107</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760033</v>
+        <v>760021</v>
       </c>
       <c r="R8" t="n">
-        <v>7093698</v>
+        <v>7093671</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,22 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,27 +1485,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477706</v>
+        <v>135477707</v>
       </c>
       <c r="B9" t="n">
-        <v>100888</v>
+        <v>103849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>222004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760044</v>
+        <v>760033</v>
       </c>
       <c r="R9" t="n">
-        <v>7093709</v>
+        <v>7093698</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,16 +1608,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477742</v>
+        <v>135477706</v>
       </c>
       <c r="B10" t="n">
-        <v>99553</v>
+        <v>100888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,16 +1625,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>222584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1624,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760136</v>
+        <v>760044</v>
       </c>
       <c r="R10" t="n">
-        <v>7093703</v>
+        <v>7093709</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,22 +1679,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,16 +1720,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477699</v>
+        <v>135477742</v>
       </c>
       <c r="B11" t="n">
-        <v>99585</v>
+        <v>99553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,38 +1737,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760132</v>
+        <v>760136</v>
       </c>
       <c r="R11" t="n">
-        <v>7093698</v>
+        <v>7093703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,22 +1791,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,16 +1832,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477700</v>
+        <v>135477699</v>
       </c>
       <c r="B12" t="n">
-        <v>99082</v>
+        <v>99585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,37 +1849,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760117</v>
+        <v>760132</v>
       </c>
       <c r="R12" t="n">
-        <v>7093700</v>
+        <v>7093698</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,16 +1948,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477743</v>
+        <v>135477700</v>
       </c>
       <c r="B13" t="n">
-        <v>103992</v>
+        <v>99082</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,16 +1965,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223284</v>
+        <v>223049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760163</v>
+        <v>760117</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,22 +2019,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,16 +2060,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477703</v>
+        <v>135477743</v>
       </c>
       <c r="B14" t="n">
-        <v>98327</v>
+        <v>103992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223358</v>
+        <v>223284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760075</v>
+        <v>760163</v>
       </c>
       <c r="R14" t="n">
-        <v>7093751</v>
+        <v>7093700</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,22 +2131,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,6 +2171,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2166,6 +2303,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,68 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135456545</v>
+        <v>135477693</v>
       </c>
       <c r="B2" t="n">
-        <v>58417</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760050</v>
+        <v>760091</v>
       </c>
       <c r="R2" t="n">
-        <v>7093705</v>
+        <v>7093644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,58 +794,62 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/135477693</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120116922</v>
+        <v>135477698</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760031</v>
+        <v>760131</v>
       </c>
       <c r="R3" t="n">
-        <v>7093709</v>
+        <v>7093695</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,12 +873,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla hack vid dike/bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,65 +908,73 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135477698</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135542830</v>
+        <v>135477692</v>
       </c>
       <c r="B4" t="n">
-        <v>8452</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760062</v>
+        <v>760037</v>
       </c>
       <c r="R4" t="n">
-        <v>7093642</v>
+        <v>7093670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,14 +1013,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1029,16 +1039,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/135477692</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126441182</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>108201</v>
+        <v>58417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,37 +1056,57 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220107</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760021</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093671</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,18 +1165,1126 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135456545</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120116922</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760031</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135542830</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännvinsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760062</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093642</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135542830</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126441182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760021</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093671</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Schneider</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126441182</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135477707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103869</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477707</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100905</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135477742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760136</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093703</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477742</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135477699</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99602</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760132</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477699</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135477700</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760117</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477700</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135477743</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104012</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>760163</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093700</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477703</t>
         </is>
       </c>
     </row>
@@ -1141,6 +2294,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135456545</v>
+        <v>120116922</v>
       </c>
       <c r="B5" t="n">
-        <v>58417</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,54 +1056,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760050</v>
+        <v>760031</v>
       </c>
       <c r="R5" t="n">
-        <v>7093705</v>
+        <v>7093709</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,27 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,69 +1134,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120116922</v>
+        <v>135542830</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>8452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760031</v>
+        <v>760062</v>
       </c>
       <c r="R6" t="n">
-        <v>7093709</v>
+        <v>7093642</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,19 +1216,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1271,65 +1246,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135542830</v>
+        <v>126441182</v>
       </c>
       <c r="B7" t="n">
-        <v>8452</v>
+        <v>108201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220107</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760062</v>
+        <v>760021</v>
       </c>
       <c r="R7" t="n">
-        <v>7093642</v>
+        <v>7093671</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,29 +1328,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1383,44 +1348,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126441182</v>
+        <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>108201</v>
+        <v>103871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220107</v>
+        <v>222004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760021</v>
+        <v>760033</v>
       </c>
       <c r="R8" t="n">
-        <v>7093671</v>
+        <v>7093698</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,12 +1430,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1460,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477707</v>
+        <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>103869</v>
+        <v>100907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,16 +1488,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222004</v>
+        <v>222584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1537,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760033</v>
+        <v>760044</v>
       </c>
       <c r="R9" t="n">
-        <v>7093698</v>
+        <v>7093709</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,16 +1583,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477706</v>
+        <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>100905</v>
+        <v>99571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222584</v>
+        <v>222812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1649,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760044</v>
+        <v>760136</v>
       </c>
       <c r="R10" t="n">
-        <v>7093709</v>
+        <v>7093703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,22 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,16 +1695,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477742</v>
+        <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99570</v>
+        <v>99603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,34 +1712,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>222857</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760136</v>
+        <v>760132</v>
       </c>
       <c r="R11" t="n">
-        <v>7093703</v>
+        <v>7093698</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,22 +1770,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,16 +1811,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477699</v>
+        <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99602</v>
+        <v>99100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,41 +1828,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760132</v>
+        <v>760117</v>
       </c>
       <c r="R12" t="n">
-        <v>7093698</v>
+        <v>7093700</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,16 +1923,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477700</v>
+        <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>99099</v>
+        <v>104014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,16 +1940,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223049</v>
+        <v>223284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760117</v>
+        <v>760163</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1994,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,16 +2035,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477743</v>
+        <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>104012</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223284</v>
+        <v>223358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760163</v>
+        <v>760075</v>
       </c>
       <c r="R14" t="n">
-        <v>7093700</v>
+        <v>7093751</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,22 +2106,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,118 +2146,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135477703</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98344</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>760075</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7093751</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2303,7 +2166,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120116922</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,38 +1056,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760031</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093709</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,65 +1165,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135456545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135542830</v>
+        <v>120116922</v>
       </c>
       <c r="B6" t="n">
-        <v>8452</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760062</v>
+        <v>760031</v>
       </c>
       <c r="R6" t="n">
-        <v>7093642</v>
+        <v>7093709</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,29 +1251,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1246,65 +1271,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126441182</v>
+        <v>135542830</v>
       </c>
       <c r="B7" t="n">
-        <v>108201</v>
+        <v>8452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220107</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760021</v>
+        <v>760062</v>
       </c>
       <c r="R7" t="n">
-        <v>7093671</v>
+        <v>7093642</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1353,29 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1348,44 +1383,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135477707</v>
+        <v>126441182</v>
       </c>
       <c r="B8" t="n">
-        <v>103871</v>
+        <v>108201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222004</v>
+        <v>220107</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760033</v>
+        <v>760021</v>
       </c>
       <c r="R8" t="n">
-        <v>7093698</v>
+        <v>7093671</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,22 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,27 +1485,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477706</v>
+        <v>135477707</v>
       </c>
       <c r="B9" t="n">
-        <v>100907</v>
+        <v>103871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>222004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760044</v>
+        <v>760033</v>
       </c>
       <c r="R9" t="n">
-        <v>7093709</v>
+        <v>7093698</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,16 +1608,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477742</v>
+        <v>135477706</v>
       </c>
       <c r="B10" t="n">
-        <v>99571</v>
+        <v>100907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,16 +1625,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>222584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1624,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760136</v>
+        <v>760044</v>
       </c>
       <c r="R10" t="n">
-        <v>7093703</v>
+        <v>7093709</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,22 +1679,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,16 +1720,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477699</v>
+        <v>135477742</v>
       </c>
       <c r="B11" t="n">
-        <v>99603</v>
+        <v>99571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,38 +1737,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760132</v>
+        <v>760136</v>
       </c>
       <c r="R11" t="n">
-        <v>7093698</v>
+        <v>7093703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,22 +1791,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,16 +1832,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477700</v>
+        <v>135477699</v>
       </c>
       <c r="B12" t="n">
-        <v>99100</v>
+        <v>99603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,37 +1849,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760117</v>
+        <v>760132</v>
       </c>
       <c r="R12" t="n">
-        <v>7093700</v>
+        <v>7093698</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,16 +1948,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477743</v>
+        <v>135477700</v>
       </c>
       <c r="B13" t="n">
-        <v>104014</v>
+        <v>99100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,16 +1965,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223284</v>
+        <v>223049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760163</v>
+        <v>760117</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,22 +2019,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,16 +2060,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477703</v>
+        <v>135477743</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>104014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223358</v>
+        <v>223284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760075</v>
+        <v>760163</v>
       </c>
       <c r="R14" t="n">
-        <v>7093751</v>
+        <v>7093700</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,22 +2131,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,6 +2171,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2166,6 +2303,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135456545</v>
+        <v>120116922</v>
       </c>
       <c r="B5" t="n">
-        <v>58417</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,54 +1056,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760050</v>
+        <v>760031</v>
       </c>
       <c r="R5" t="n">
-        <v>7093705</v>
+        <v>7093709</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,27 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,69 +1134,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120116922</v>
+        <v>135542830</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>8452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760031</v>
+        <v>760062</v>
       </c>
       <c r="R6" t="n">
-        <v>7093709</v>
+        <v>7093642</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,19 +1216,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1271,65 +1246,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135542830</v>
+        <v>126441182</v>
       </c>
       <c r="B7" t="n">
-        <v>8452</v>
+        <v>108201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220107</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760062</v>
+        <v>760021</v>
       </c>
       <c r="R7" t="n">
-        <v>7093642</v>
+        <v>7093671</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,29 +1328,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1383,44 +1348,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126441182</v>
+        <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>108201</v>
+        <v>103871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220107</v>
+        <v>222004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760021</v>
+        <v>760033</v>
       </c>
       <c r="R8" t="n">
-        <v>7093671</v>
+        <v>7093698</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,12 +1430,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1460,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477707</v>
+        <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>103871</v>
+        <v>100907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,16 +1488,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222004</v>
+        <v>222584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1537,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760033</v>
+        <v>760044</v>
       </c>
       <c r="R9" t="n">
-        <v>7093698</v>
+        <v>7093709</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,16 +1583,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477706</v>
+        <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>100907</v>
+        <v>99571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222584</v>
+        <v>222812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1649,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760044</v>
+        <v>760136</v>
       </c>
       <c r="R10" t="n">
-        <v>7093709</v>
+        <v>7093703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,22 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,16 +1695,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477742</v>
+        <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99571</v>
+        <v>99603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,34 +1712,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>222857</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760136</v>
+        <v>760132</v>
       </c>
       <c r="R11" t="n">
-        <v>7093703</v>
+        <v>7093698</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,22 +1770,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,16 +1811,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477699</v>
+        <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99603</v>
+        <v>99100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,41 +1828,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760132</v>
+        <v>760117</v>
       </c>
       <c r="R12" t="n">
-        <v>7093698</v>
+        <v>7093700</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,16 +1923,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477700</v>
+        <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>99100</v>
+        <v>104014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,16 +1940,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223049</v>
+        <v>223284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760117</v>
+        <v>760163</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1994,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,16 +2035,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477743</v>
+        <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>104014</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223284</v>
+        <v>223358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760163</v>
+        <v>760075</v>
       </c>
       <c r="R14" t="n">
-        <v>7093700</v>
+        <v>7093751</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,22 +2106,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,118 +2146,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135477703</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>760075</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7093751</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2303,7 +2166,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120116922</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,38 +1056,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760031</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093709</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,65 +1165,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135456545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135542830</v>
+        <v>120116922</v>
       </c>
       <c r="B6" t="n">
-        <v>8452</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760062</v>
+        <v>760031</v>
       </c>
       <c r="R6" t="n">
-        <v>7093642</v>
+        <v>7093709</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,29 +1251,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1246,65 +1271,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126441182</v>
+        <v>135542830</v>
       </c>
       <c r="B7" t="n">
-        <v>108201</v>
+        <v>8452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220107</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760021</v>
+        <v>760062</v>
       </c>
       <c r="R7" t="n">
-        <v>7093671</v>
+        <v>7093642</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1353,29 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1348,44 +1383,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135477707</v>
+        <v>126441182</v>
       </c>
       <c r="B8" t="n">
-        <v>103871</v>
+        <v>108201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222004</v>
+        <v>220107</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760033</v>
+        <v>760021</v>
       </c>
       <c r="R8" t="n">
-        <v>7093698</v>
+        <v>7093671</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,22 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,27 +1485,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477706</v>
+        <v>135477707</v>
       </c>
       <c r="B9" t="n">
-        <v>100907</v>
+        <v>103871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>222004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760044</v>
+        <v>760033</v>
       </c>
       <c r="R9" t="n">
-        <v>7093709</v>
+        <v>7093698</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,16 +1608,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477742</v>
+        <v>135477706</v>
       </c>
       <c r="B10" t="n">
-        <v>99571</v>
+        <v>100907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,16 +1625,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>222584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1624,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760136</v>
+        <v>760044</v>
       </c>
       <c r="R10" t="n">
-        <v>7093703</v>
+        <v>7093709</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,22 +1679,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,16 +1720,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477699</v>
+        <v>135477742</v>
       </c>
       <c r="B11" t="n">
-        <v>99603</v>
+        <v>99571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,38 +1737,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760132</v>
+        <v>760136</v>
       </c>
       <c r="R11" t="n">
-        <v>7093698</v>
+        <v>7093703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,22 +1791,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,16 +1832,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477700</v>
+        <v>135477699</v>
       </c>
       <c r="B12" t="n">
-        <v>99100</v>
+        <v>99603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,37 +1849,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760117</v>
+        <v>760132</v>
       </c>
       <c r="R12" t="n">
-        <v>7093700</v>
+        <v>7093698</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,16 +1948,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477743</v>
+        <v>135477700</v>
       </c>
       <c r="B13" t="n">
-        <v>104014</v>
+        <v>99100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,16 +1965,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223284</v>
+        <v>223049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760163</v>
+        <v>760117</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,22 +2019,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,16 +2060,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477703</v>
+        <v>135477743</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>104014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223358</v>
+        <v>223284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760075</v>
+        <v>760163</v>
       </c>
       <c r="R14" t="n">
-        <v>7093751</v>
+        <v>7093700</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,22 +2131,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,6 +2171,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2166,6 +2303,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58418</v>
+        <v>58422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58422</v>
+        <v>58423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135456545</v>
+        <v>120116922</v>
       </c>
       <c r="B5" t="n">
-        <v>58423</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,54 +1056,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760050</v>
+        <v>760031</v>
       </c>
       <c r="R5" t="n">
-        <v>7093705</v>
+        <v>7093709</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,27 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,69 +1134,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456545</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120116922</v>
+        <v>135542830</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>8452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760031</v>
+        <v>760062</v>
       </c>
       <c r="R6" t="n">
-        <v>7093709</v>
+        <v>7093642</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,19 +1216,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1271,65 +1246,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135542830</v>
+        <v>126441182</v>
       </c>
       <c r="B7" t="n">
-        <v>8452</v>
+        <v>108201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220107</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760062</v>
+        <v>760021</v>
       </c>
       <c r="R7" t="n">
-        <v>7093642</v>
+        <v>7093671</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,29 +1328,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1383,44 +1348,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126441182</v>
+        <v>135477707</v>
       </c>
       <c r="B8" t="n">
-        <v>108201</v>
+        <v>103871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220107</v>
+        <v>222004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760021</v>
+        <v>760033</v>
       </c>
       <c r="R8" t="n">
-        <v>7093671</v>
+        <v>7093698</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,12 +1430,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1460,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477707</v>
+        <v>135477706</v>
       </c>
       <c r="B9" t="n">
-        <v>103871</v>
+        <v>100907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,16 +1488,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222004</v>
+        <v>222584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1537,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760033</v>
+        <v>760044</v>
       </c>
       <c r="R9" t="n">
-        <v>7093698</v>
+        <v>7093709</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,16 +1583,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477706</v>
+        <v>135477742</v>
       </c>
       <c r="B10" t="n">
-        <v>100907</v>
+        <v>99571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222584</v>
+        <v>222812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1649,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760044</v>
+        <v>760136</v>
       </c>
       <c r="R10" t="n">
-        <v>7093709</v>
+        <v>7093703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,22 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,16 +1695,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477742</v>
+        <v>135477699</v>
       </c>
       <c r="B11" t="n">
-        <v>99571</v>
+        <v>99603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,34 +1712,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>222857</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760136</v>
+        <v>760132</v>
       </c>
       <c r="R11" t="n">
-        <v>7093703</v>
+        <v>7093698</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,22 +1770,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,16 +1811,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477699</v>
+        <v>135477700</v>
       </c>
       <c r="B12" t="n">
-        <v>99603</v>
+        <v>99100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,41 +1828,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222857</v>
+        <v>223049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760132</v>
+        <v>760117</v>
       </c>
       <c r="R12" t="n">
-        <v>7093698</v>
+        <v>7093700</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,16 +1923,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477700</v>
+        <v>135477743</v>
       </c>
       <c r="B13" t="n">
-        <v>99100</v>
+        <v>104014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,16 +1940,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223049</v>
+        <v>223284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760117</v>
+        <v>760163</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1994,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,16 +2035,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477743</v>
+        <v>135477703</v>
       </c>
       <c r="B14" t="n">
-        <v>104014</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223284</v>
+        <v>223358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760163</v>
+        <v>760075</v>
       </c>
       <c r="R14" t="n">
-        <v>7093700</v>
+        <v>7093751</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,22 +2106,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,118 +2146,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135477703</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>760075</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7093751</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2303,7 +2166,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120116922</v>
+        <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,38 +1056,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760031</v>
+        <v>760050</v>
       </c>
       <c r="R5" t="n">
-        <v>7093709</v>
+        <v>7093705</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1130,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Båda föräldrarna närvarande. Ena föräldern gjorde skenattacker mot mig med mat i munnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,65 +1165,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135456545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135542830</v>
+        <v>120116922</v>
       </c>
       <c r="B6" t="n">
-        <v>8452</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännvinsmyran, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760062</v>
+        <v>760031</v>
       </c>
       <c r="R6" t="n">
-        <v>7093642</v>
+        <v>7093709</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,29 +1251,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1246,65 +1271,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135542830</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126441182</v>
+        <v>135542830</v>
       </c>
       <c r="B7" t="n">
-        <v>108201</v>
+        <v>8452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220107</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Brännvinsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760021</v>
+        <v>760062</v>
       </c>
       <c r="R7" t="n">
-        <v>7093671</v>
+        <v>7093642</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,19 +1353,29 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1348,44 +1383,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126441182</t>
+          <t>https://artportalen.se/Sighting/135542830</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135477707</v>
+        <v>126441182</v>
       </c>
       <c r="B8" t="n">
-        <v>103871</v>
+        <v>108201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222004</v>
+        <v>220107</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760033</v>
+        <v>760021</v>
       </c>
       <c r="R8" t="n">
-        <v>7093698</v>
+        <v>7093671</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,22 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,27 +1485,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477707</t>
+          <t>https://artportalen.se/Sighting/126441182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135477706</v>
+        <v>135477707</v>
       </c>
       <c r="B9" t="n">
-        <v>100907</v>
+        <v>103871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>222004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760044</v>
+        <v>760033</v>
       </c>
       <c r="R9" t="n">
-        <v>7093709</v>
+        <v>7093698</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,16 +1608,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
+          <t>https://artportalen.se/Sighting/135477707</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135477742</v>
+        <v>135477706</v>
       </c>
       <c r="B10" t="n">
-        <v>99571</v>
+        <v>100907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,16 +1625,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>222584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1624,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760136</v>
+        <v>760044</v>
       </c>
       <c r="R10" t="n">
-        <v>7093703</v>
+        <v>7093709</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,22 +1679,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,16 +1720,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477742</t>
+          <t>https://artportalen.se/Sighting/135477706</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135477699</v>
+        <v>135477742</v>
       </c>
       <c r="B11" t="n">
-        <v>99603</v>
+        <v>99571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,38 +1737,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760132</v>
+        <v>760136</v>
       </c>
       <c r="R11" t="n">
-        <v>7093698</v>
+        <v>7093703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,22 +1791,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,16 +1832,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477699</t>
+          <t>https://artportalen.se/Sighting/135477742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477700</v>
+        <v>135477699</v>
       </c>
       <c r="B12" t="n">
-        <v>99100</v>
+        <v>99603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,37 +1849,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223049</v>
+        <v>222857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760117</v>
+        <v>760132</v>
       </c>
       <c r="R12" t="n">
-        <v>7093700</v>
+        <v>7093698</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,16 +1948,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477700</t>
+          <t>https://artportalen.se/Sighting/135477699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477743</v>
+        <v>135477700</v>
       </c>
       <c r="B13" t="n">
-        <v>104014</v>
+        <v>99100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,16 +1965,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223284</v>
+        <v>223049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,13 +1989,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760163</v>
+        <v>760117</v>
       </c>
       <c r="R13" t="n">
         <v>7093700</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,22 +2019,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,16 +2060,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477743</t>
+          <t>https://artportalen.se/Sighting/135477700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477703</v>
+        <v>135477743</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>104014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223358</v>
+        <v>223284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760075</v>
+        <v>760163</v>
       </c>
       <c r="R14" t="n">
-        <v>7093751</v>
+        <v>7093700</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,22 +2131,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,6 +2171,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477743</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135477703</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760075</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7093751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135477703</t>
         </is>
@@ -2166,6 +2303,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42835-2025 artfynd.xlsx
+++ b/artfynd/A 42835-2025 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>135456545</v>
       </c>
       <c r="B5" t="n">
-        <v>58428</v>
+        <v>58441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
